--- a/data/trans_camb/P2B_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,22; 35,5</t>
+          <t>20,72; 35,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,07; 26,39</t>
+          <t>11,76; 26,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 3,13</t>
+          <t>-9,37; 3,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,43; 38,9</t>
+          <t>21,69; 38,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,58; 31,74</t>
+          <t>15,32; 32,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,41; 2,44</t>
+          <t>-12,11; 1,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,97; 34,75</t>
+          <t>23,35; 35,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,21; 27,46</t>
+          <t>16,45; 27,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 0,51</t>
+          <t>-8,24; 0,79</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>83,42; 188,17</t>
+          <t>82,84; 196,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41,24; 136,44</t>
+          <t>47,34; 141,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-36,56; 17,21</t>
+          <t>-38,04; 18,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67,26; 168,38</t>
+          <t>68,63; 170,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>50,57; 139,46</t>
+          <t>45,46; 137,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,56; 10,59</t>
+          <t>-38,06; 9,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,3; 162,86</t>
+          <t>85,63; 158,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>60,83; 129,39</t>
+          <t>60,56; 126,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-31,18; 2,46</t>
+          <t>-31,04; 3,77</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,71; 35,12</t>
+          <t>19,36; 35,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,68; 32,7</t>
+          <t>16,2; 32,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 5,02</t>
+          <t>-9,3; 4,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25,25; 40,84</t>
+          <t>24,49; 40,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,9; 34,11</t>
+          <t>18,42; 34,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,81; 1,04</t>
+          <t>-12,35; 0,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,99; 35,17</t>
+          <t>24,11; 35,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,38; 30,87</t>
+          <t>20,26; 31,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 0,82</t>
+          <t>-8,76; 0,64</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>72,72; 192,57</t>
+          <t>71,91; 201,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>60,86; 178,6</t>
+          <t>60,72; 181,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-35,3; 27,37</t>
+          <t>-35,08; 26,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72,97; 161,71</t>
+          <t>72,0; 154,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>53,14; 135,03</t>
+          <t>53,04; 129,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-37,54; 4,54</t>
+          <t>-36,53; 3,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,82; 147,57</t>
+          <t>83,38; 151,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>66,21; 130,88</t>
+          <t>70,22; 135,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-30,63; 3,72</t>
+          <t>-30,94; 2,63</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,93; 34,27</t>
+          <t>22,35; 34,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,38; 25,87</t>
+          <t>13,73; 26,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 10,62</t>
+          <t>-2,17; 10,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,67; 34,27</t>
+          <t>14,44; 34,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,05; 26,79</t>
+          <t>2,7; 26,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,04; 3,81</t>
+          <t>-15,06; 4,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,08; 32,37</t>
+          <t>22,03; 32,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,48; 24,22</t>
+          <t>13,02; 24,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 7,35</t>
+          <t>-3,18; 6,89</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>83,32; 172,79</t>
+          <t>86,06; 174,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>50,92; 130,39</t>
+          <t>51,11; 136,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 51,02</t>
+          <t>-8,19; 53,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35,58; 147,06</t>
+          <t>37,99; 151,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,55; 117,02</t>
+          <t>7,81; 116,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-44,91; 15,14</t>
+          <t>-43,02; 17,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>79,79; 147,01</t>
+          <t>81,71; 150,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>47,84; 110,45</t>
+          <t>48,1; 109,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 33,93</t>
+          <t>-12,58; 32,14</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>28,6; 36,94</t>
+          <t>28,26; 36,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,07; 21,43</t>
+          <t>13,2; 21,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 7,65</t>
+          <t>-1,45; 7,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29,17; 40,12</t>
+          <t>29,73; 40,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,0; 32,34</t>
+          <t>22,11; 32,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 49,21</t>
+          <t>-4,47; 46,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,49; 36,71</t>
+          <t>30,38; 36,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,72; 25,68</t>
+          <t>18,64; 25,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 34,61</t>
+          <t>-0,14; 37,98</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>119,53; 186,08</t>
+          <t>115,25; 181,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>55,02; 109,46</t>
+          <t>55,56; 106,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 37,96</t>
+          <t>-6,57; 36,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>103,03; 172,09</t>
+          <t>101,06; 173,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>76,26; 140,38</t>
+          <t>77,14; 142,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-17,75; 199,76</t>
+          <t>-16,62; 188,99</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>120,51; 167,89</t>
+          <t>119,97; 167,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>73,96; 116,31</t>
+          <t>73,21; 113,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 151,01</t>
+          <t>-1,08; 167,27</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>22,05; 36,51</t>
+          <t>22,42; 37,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14,02; 27,64</t>
+          <t>14,19; 27,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 6,04</t>
+          <t>-7,54; 5,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25,7; 36,46</t>
+          <t>25,91; 36,84</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,97; 26,22</t>
+          <t>15,08; 25,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 6,25</t>
+          <t>-8,15; 6,88</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,19; 34,74</t>
+          <t>25,45; 34,62</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16,16; 24,95</t>
+          <t>15,69; 24,84</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 4,52</t>
+          <t>-6,38; 4,29</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>83,08; 204,28</t>
+          <t>80,35; 202,61</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>52,0; 153,79</t>
+          <t>50,96; 154,35</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-30,78; 33,77</t>
+          <t>-29,11; 30,81</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>88,55; 161,09</t>
+          <t>88,1; 163,14</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>49,84; 115,55</t>
+          <t>51,64; 113,34</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-30,02; 25,7</t>
+          <t>-28,52; 28,98</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,41; 160,6</t>
+          <t>91,01; 156,34</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>58,95; 115,78</t>
+          <t>57,4; 111,15</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-21,01; 20,33</t>
+          <t>-24,8; 18,76</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>19,63; 40,1</t>
+          <t>19,27; 40,67</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>11,2; 30,31</t>
+          <t>10,67; 30,79</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 13,62</t>
+          <t>-10,35; 13,68</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15,28; 23,63</t>
+          <t>15,29; 23,79</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>9,31; 18,36</t>
+          <t>9,26; 17,74</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,96; 13,46</t>
+          <t>4,6; 13,03</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,91; 24,4</t>
+          <t>17,03; 24,87</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>10,61; 18,42</t>
+          <t>10,57; 18,4</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3,51; 11,64</t>
+          <t>3,43; 11,69</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>83,64; 342,37</t>
+          <t>80,97; 348,78</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>47,6; 245,28</t>
+          <t>47,39; 264,43</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-55,29; 99,99</t>
+          <t>-50,38; 98,01</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>58,54; 104,41</t>
+          <t>57,19; 103,85</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>35,2; 80,63</t>
+          <t>35,12; 76,6</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18,47; 58,29</t>
+          <t>17,37; 57,91</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>65,68; 111,46</t>
+          <t>66,29; 112,75</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>42,21; 84,42</t>
+          <t>41,43; 82,89</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>13,62; 52,81</t>
+          <t>13,49; 53,02</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>27,38; 32,35</t>
+          <t>27,35; 32,38</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>16,85; 22,23</t>
+          <t>17,0; 22,45</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 3,29</t>
+          <t>-1,77; 3,41</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>25,67; 30,54</t>
+          <t>25,3; 30,3</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>18,34; 23,4</t>
+          <t>18,27; 23,17</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 21,86</t>
+          <t>-0,46; 22,43</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,0; 30,64</t>
+          <t>27,13; 30,65</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>18,47; 21,98</t>
+          <t>18,59; 22,06</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 14,49</t>
+          <t>-0,07; 15,85</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>119,53; 157,3</t>
+          <t>117,29; 156,96</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>72,62; 108,41</t>
+          <t>73,46; 108,1</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 15,69</t>
+          <t>-7,57; 16,34</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>93,68; 122,9</t>
+          <t>92,08; 121,45</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>66,82; 94,53</t>
+          <t>66,74; 92,63</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 86,64</t>
+          <t>-1,77; 87,95</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>107,71; 131,58</t>
+          <t>107,81; 131,32</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>73,96; 94,44</t>
+          <t>73,89; 94,27</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 60,95</t>
+          <t>-0,45; 64,32</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2B_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-3,2</t>
+          <t>-2,09</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-4,94</t>
+          <t>-4,76</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-3,66</t>
+          <t>-2,99</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,72; 35,5</t>
+          <t>20,85; 35,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,76; 26,22</t>
+          <t>11,14; 26,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 3,54</t>
+          <t>-8,72; 3,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,69; 38,57</t>
+          <t>21,42; 38,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,32; 32,19</t>
+          <t>15,98; 33,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 1,81</t>
+          <t>-11,7; 1,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,35; 35,02</t>
+          <t>23,97; 34,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,45; 27,31</t>
+          <t>16,71; 27,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 0,79</t>
+          <t>-7,56; 1,75</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-14,5%</t>
+          <t>-9,5%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-18,18%</t>
+          <t>-17,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-15,18%</t>
+          <t>-12,4%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>82,84; 196,15</t>
+          <t>82,14; 192,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47,34; 141,76</t>
+          <t>43,31; 137,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-38,04; 18,65</t>
+          <t>-34,87; 17,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68,63; 170,83</t>
+          <t>67,62; 172,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>45,46; 137,81</t>
+          <t>50,77; 149,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,06; 9,25</t>
+          <t>-37,38; 8,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,63; 158,79</t>
+          <t>89,22; 162,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>60,56; 126,15</t>
+          <t>60,96; 127,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-31,04; 3,77</t>
+          <t>-28,07; 9,11</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,0</t>
+          <t>-1,07</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-5,86</t>
+          <t>-5,45</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-4,16</t>
+          <t>-3,45</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,36; 35,85</t>
+          <t>20,1; 35,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,2; 32,15</t>
+          <t>15,86; 32,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 4,63</t>
+          <t>-8,8; 5,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,49; 40,22</t>
+          <t>24,22; 41,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,42; 34,21</t>
+          <t>18,35; 34,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 0,92</t>
+          <t>-12,28; 0,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,11; 35,36</t>
+          <t>23,22; 34,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,26; 31,0</t>
+          <t>20,0; 31,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 0,64</t>
+          <t>-8,59; 1,51</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-9,06%</t>
+          <t>-4,84%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-19,52%</t>
+          <t>-18,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-15,86%</t>
+          <t>-13,16%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>71,91; 201,97</t>
+          <t>72,81; 193,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>60,72; 181,79</t>
+          <t>58,34; 176,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-35,08; 26,6</t>
+          <t>-33,26; 31,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72,0; 154,91</t>
+          <t>70,14; 156,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>53,04; 129,49</t>
+          <t>52,3; 132,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-36,53; 3,69</t>
+          <t>-34,82; 4,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,38; 151,91</t>
+          <t>78,43; 148,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>70,22; 135,92</t>
+          <t>67,44; 136,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-30,94; 2,63</t>
+          <t>-29,49; 6,37</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,51</t>
+          <t>5,13</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-5,19</t>
+          <t>-5,36</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,85</t>
+          <t>2,24</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,35; 34,27</t>
+          <t>22,04; 34,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,73; 26,73</t>
+          <t>13,79; 26,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 10,64</t>
+          <t>-1,1; 12,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,44; 34,65</t>
+          <t>13,78; 33,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 26,11</t>
+          <t>2,92; 26,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,06; 4,12</t>
+          <t>-14,95; 3,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,03; 32,65</t>
+          <t>22,33; 32,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,02; 24,17</t>
+          <t>13,37; 23,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 6,89</t>
+          <t>-2,66; 7,43</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-17,8%</t>
+          <t>-18,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>86,06; 174,31</t>
+          <t>83,76; 173,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51,11; 136,23</t>
+          <t>51,68; 129,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 53,85</t>
+          <t>-4,75; 58,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>37,99; 151,52</t>
+          <t>38,38; 143,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,81; 116,41</t>
+          <t>7,9; 112,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-43,02; 17,94</t>
+          <t>-43,3; 18,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>81,71; 150,48</t>
+          <t>81,08; 151,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>48,1; 109,09</t>
+          <t>47,89; 109,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 32,14</t>
+          <t>-10,51; 33,12</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,29</t>
+          <t>4,64</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,86</t>
+          <t>-2,68</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11,07</t>
+          <t>1,62</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>28,26; 36,67</t>
+          <t>28,35; 36,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,2; 21,75</t>
+          <t>13,15; 22,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 7,41</t>
+          <t>0,61; 9,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29,73; 40,29</t>
+          <t>29,92; 40,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,11; 32,87</t>
+          <t>22,27; 33,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 46,05</t>
+          <t>-7,26; 1,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,38; 36,96</t>
+          <t>30,34; 37,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,64; 25,16</t>
+          <t>18,88; 25,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 37,98</t>
+          <t>-1,32; 4,77</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>-10,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>115,25; 181,57</t>
+          <t>118,23; 186,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>55,56; 106,56</t>
+          <t>55,02; 108,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 36,34</t>
+          <t>2,71; 45,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>101,06; 173,83</t>
+          <t>102,31; 173,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>77,14; 142,91</t>
+          <t>77,91; 144,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-16,62; 188,99</t>
+          <t>-25,14; 6,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>119,97; 167,54</t>
+          <t>120,2; 167,67</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>73,21; 113,51</t>
+          <t>74,84; 115,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 167,27</t>
+          <t>-5,19; 21,31</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-1,15</t>
+          <t>-1,23</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>5,75</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>3,16</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>22,42; 37,18</t>
+          <t>21,89; 36,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14,19; 27,78</t>
+          <t>14,19; 28,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 5,47</t>
+          <t>-8,22; 5,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25,91; 36,84</t>
+          <t>25,32; 36,57</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,08; 25,67</t>
+          <t>14,8; 26,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 6,88</t>
+          <t>0,92; 11,05</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,45; 34,62</t>
+          <t>26,22; 34,9</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15,69; 24,84</t>
+          <t>16,1; 24,85</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 4,29</t>
+          <t>-0,87; 6,95</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-5,16%</t>
+          <t>-5,55%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>80,35; 202,61</t>
+          <t>83,17; 199,61</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>50,96; 154,35</t>
+          <t>54,06; 155,57</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-29,11; 30,81</t>
+          <t>-32,05; 29,65</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>88,1; 163,14</t>
+          <t>85,78; 162,88</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>51,64; 113,34</t>
+          <t>52,29; 117,36</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-28,52; 28,98</t>
+          <t>2,76; 49,16</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,01; 156,34</t>
+          <t>95,05; 157,24</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>57,4; 111,15</t>
+          <t>59,32; 112,55</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-24,8; 18,76</t>
+          <t>-3,58; 31,17</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>6,86</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,09</t>
+          <t>9,66</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7,43</t>
+          <t>9,15</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>19,27; 40,67</t>
+          <t>19,69; 39,23</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>10,67; 30,79</t>
+          <t>10,42; 30,1</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 13,68</t>
+          <t>-4,66; 22,65</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15,29; 23,79</t>
+          <t>15,16; 23,8</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>9,26; 17,74</t>
+          <t>9,48; 18,23</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,6; 13,03</t>
+          <t>5,65; 13,93</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,03; 24,87</t>
+          <t>16,92; 24,78</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>10,57; 18,4</t>
+          <t>10,46; 18,51</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3,43; 11,69</t>
+          <t>4,92; 13,19</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>38,5%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>80,97; 348,78</t>
+          <t>89,66; 306,38</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>47,39; 264,43</t>
+          <t>45,87; 249,65</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-50,38; 98,01</t>
+          <t>-25,27; 176,81</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>57,19; 103,85</t>
+          <t>57,12; 105,25</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>35,12; 76,6</t>
+          <t>35,53; 79,88</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,37; 57,91</t>
+          <t>21,29; 60,12</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>66,29; 112,75</t>
+          <t>66,05; 113,73</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>41,43; 82,89</t>
+          <t>40,3; 81,22</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>13,49; 53,02</t>
+          <t>19,22; 59,33</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>2,02</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,53</t>
+          <t>1,77</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3,66</t>
+          <t>1,92</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>27,35; 32,38</t>
+          <t>27,46; 32,5</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>17,0; 22,45</t>
+          <t>17,36; 22,59</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 3,41</t>
+          <t>-0,84; 4,27</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>25,3; 30,3</t>
+          <t>25,56; 30,61</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>18,27; 23,17</t>
+          <t>18,14; 23,35</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 22,43</t>
+          <t>-0,47; 3,95</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,13; 30,65</t>
+          <t>27,03; 30,66</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>18,59; 22,06</t>
+          <t>18,58; 22,08</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 15,85</t>
+          <t>0,14; 3,52</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>117,29; 156,96</t>
+          <t>117,98; 158,96</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>73,46; 108,1</t>
+          <t>74,16; 108,18</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 16,34</t>
+          <t>-3,54; 20,94</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>92,08; 121,45</t>
+          <t>91,9; 123,09</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>66,74; 92,63</t>
+          <t>65,53; 92,34</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 87,95</t>
+          <t>-1,82; 15,68</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>107,81; 131,32</t>
+          <t>107,75; 131,68</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>73,89; 94,27</t>
+          <t>73,43; 94,39</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 64,32</t>
+          <t>0,62; 15,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2B_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Clase-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales</t>
+          <t>Población que convive con personas que requieren dedicación o cuidados especiales</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
